--- a/Assignment 2 - Data Cleaning and Transformation.xlsx
+++ b/Assignment 2 - Data Cleaning and Transformation.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Raw data" sheetId="2" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="Sheet3" sheetId="12" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="3" hidden="1">'cleaned Data'!$A$1:$H$36</definedName>
+    <definedName name="ExternalData_1" localSheetId="3" hidden="1">'cleaned Data'!$A$1:$G$36</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="199">
   <si>
     <t>Product ID</t>
   </si>
@@ -861,7 +861,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -912,9 +912,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -923,26 +920,7 @@
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="40">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="39">
     <dxf>
       <font>
         <b val="0"/>
@@ -1739,25 +1717,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
-      <tableStyleElement type="wholeTable" dxfId="39"/>
-      <tableStyleElement type="headerRow" dxfId="38"/>
-      <tableStyleElement type="totalRow" dxfId="37"/>
-      <tableStyleElement type="firstColumn" dxfId="36"/>
-      <tableStyleElement type="lastColumn" dxfId="35"/>
-      <tableStyleElement type="firstRowStripe" dxfId="34"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="33"/>
+      <tableStyleElement type="wholeTable" dxfId="38"/>
+      <tableStyleElement type="headerRow" dxfId="37"/>
+      <tableStyleElement type="totalRow" dxfId="36"/>
+      <tableStyleElement type="firstColumn" dxfId="35"/>
+      <tableStyleElement type="lastColumn" dxfId="34"/>
+      <tableStyleElement type="firstRowStripe" dxfId="33"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="32"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
-      <tableStyleElement type="headerRow" dxfId="32"/>
-      <tableStyleElement type="totalRow" dxfId="31"/>
-      <tableStyleElement type="firstRowStripe" dxfId="30"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="29"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="28"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="27"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="26"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="25"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="24"/>
-      <tableStyleElement type="pageFieldValues" dxfId="23"/>
+      <tableStyleElement type="headerRow" dxfId="31"/>
+      <tableStyleElement type="totalRow" dxfId="30"/>
+      <tableStyleElement type="firstRowStripe" dxfId="29"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="28"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="27"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="26"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="25"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="24"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="23"/>
+      <tableStyleElement type="pageFieldValues" dxfId="22"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2068,49 +2046,50 @@
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ExternalData_1" connectionId="1" autoFormatId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh preserveSortFilterLayout="0" nextId="9">
-    <queryTableFields count="8">
+    <queryTableFields count="7">
       <queryTableField id="1" name="Manufacturing Date" tableColumnId="17"/>
       <queryTableField id="2" name="Country Code" tableColumnId="18"/>
       <queryTableField id="3" name="Product Brand" tableColumnId="19"/>
-      <queryTableField id="4" name="Price ($)" tableColumnId="20"/>
       <queryTableField id="5" name="Quantity" tableColumnId="21"/>
       <queryTableField id="6" name="Category" tableColumnId="22"/>
       <queryTableField id="7" name="PRICE ($)2" tableColumnId="23"/>
       <queryTableField id="8" name="D/M/Y" tableColumnId="24"/>
     </queryTableFields>
+    <queryTableDeletedFields count="1">
+      <deletedField name="Price ($)"/>
+    </queryTableDeletedFields>
   </queryTableRefresh>
 </queryTable>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J36" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19" totalsRowBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J36" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18" totalsRowBorderDxfId="17">
   <autoFilter ref="A1:J36"/>
   <tableColumns count="10">
-    <tableColumn id="1" name="Product ID" dataDxfId="17"/>
-    <tableColumn id="2" name="Product Name" dataDxfId="16"/>
-    <tableColumn id="3" name="Brand Name" dataDxfId="15"/>
-    <tableColumn id="4" name="Price ($)" dataDxfId="14"/>
-    <tableColumn id="5" name="Quantity" dataDxfId="13"/>
-    <tableColumn id="6" name="Category" dataDxfId="12"/>
-    <tableColumn id="7" name="PRICE ($)2" dataDxfId="11">
+    <tableColumn id="1" name="Product ID" dataDxfId="16"/>
+    <tableColumn id="2" name="Product Name" dataDxfId="15"/>
+    <tableColumn id="3" name="Brand Name" dataDxfId="14"/>
+    <tableColumn id="4" name="Price ($)" dataDxfId="13"/>
+    <tableColumn id="5" name="Quantity" dataDxfId="12"/>
+    <tableColumn id="6" name="Category" dataDxfId="11"/>
+    <tableColumn id="7" name="PRICE ($)2" dataDxfId="10">
       <calculatedColumnFormula>IF(D2="",AVERAGEIF($F$2:$F$36,F2,$D$2:$D$36),D2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" name="DATE" dataDxfId="10"/>
-    <tableColumn id="9" name="MONTH" dataDxfId="9"/>
-    <tableColumn id="10" name="YEAR" dataDxfId="8"/>
+    <tableColumn id="8" name="DATE" dataDxfId="9"/>
+    <tableColumn id="9" name="MONTH" dataDxfId="8"/>
+    <tableColumn id="10" name="YEAR" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStylePreset3_Accent1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table1__2" displayName="Table1__2" ref="A1:H36" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:H36"/>
-  <tableColumns count="8">
-    <tableColumn id="17" uniqueName="17" name="Manufacturing Date" queryTableFieldId="1" dataDxfId="7"/>
-    <tableColumn id="18" uniqueName="18" name="Country Code" queryTableFieldId="2" dataDxfId="6"/>
-    <tableColumn id="19" uniqueName="19" name="Product Brand" queryTableFieldId="3" dataDxfId="5"/>
-    <tableColumn id="20" uniqueName="20" name="Price ($)" queryTableFieldId="4" dataDxfId="4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table1__2" displayName="Table1__2" ref="A1:G36" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G36"/>
+  <tableColumns count="7">
+    <tableColumn id="17" uniqueName="17" name="Manufacturing Date" queryTableFieldId="1" dataDxfId="6"/>
+    <tableColumn id="18" uniqueName="18" name="Country Code" queryTableFieldId="2" dataDxfId="5"/>
+    <tableColumn id="19" uniqueName="19" name="Product Brand" queryTableFieldId="3" dataDxfId="4"/>
     <tableColumn id="21" uniqueName="21" name="Quantity" queryTableFieldId="5" dataDxfId="3"/>
     <tableColumn id="22" uniqueName="22" name="Category" queryTableFieldId="6" dataDxfId="2"/>
     <tableColumn id="23" uniqueName="23" name="PRICE ($)2" queryTableFieldId="7" dataDxfId="1"/>
@@ -5318,7 +5297,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="18.140625" customWidth="1"/>
@@ -5331,7 +5310,7 @@
     <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="33" t="s">
         <v>101</v>
       </c>
@@ -5342,22 +5321,19 @@
         <v>103</v>
       </c>
       <c r="D1" s="33" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" s="33" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" s="33" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="G1" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="H1" s="33" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:7">
       <c r="A2" s="33">
         <v>28</v>
       </c>
@@ -5367,23 +5343,20 @@
       <c r="C2" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="34">
+      <c r="D2" s="33">
+        <v>30</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="34">
         <v>1000</v>
       </c>
-      <c r="E2" s="33">
-        <v>30</v>
-      </c>
-      <c r="F2" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="35">
-        <v>1000</v>
-      </c>
-      <c r="H2" s="33" t="s">
+      <c r="G2" s="33" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:7">
       <c r="A3" s="33">
         <v>15</v>
       </c>
@@ -5394,22 +5367,19 @@
         <v>106</v>
       </c>
       <c r="D3" s="33">
+        <v>15</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="34">
         <v>80</v>
       </c>
-      <c r="E3" s="33">
-        <v>15</v>
-      </c>
-      <c r="F3" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="35">
-        <v>80</v>
-      </c>
-      <c r="H3" s="33" t="s">
+      <c r="G3" s="33" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:7">
       <c r="A4" s="33">
         <v>3</v>
       </c>
@@ -5420,22 +5390,19 @@
         <v>107</v>
       </c>
       <c r="D4" s="33">
+        <v>40</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="34">
         <v>130</v>
       </c>
-      <c r="E4" s="33">
-        <v>40</v>
-      </c>
-      <c r="F4" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="35">
-        <v>130</v>
-      </c>
-      <c r="H4" s="33" t="s">
+      <c r="G4" s="33" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:7">
       <c r="A5" s="33">
         <v>11</v>
       </c>
@@ -5446,22 +5413,19 @@
         <v>108</v>
       </c>
       <c r="D5" s="33">
+        <v>25</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="34">
         <v>900</v>
       </c>
-      <c r="E5" s="33">
-        <v>25</v>
-      </c>
-      <c r="F5" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="35">
-        <v>900</v>
-      </c>
-      <c r="H5" s="33" t="s">
+      <c r="G5" s="33" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:7">
       <c r="A6" s="33">
         <v>22</v>
       </c>
@@ -5472,22 +5436,19 @@
         <v>109</v>
       </c>
       <c r="D6" s="33">
+        <v>20</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="34">
         <v>70</v>
       </c>
-      <c r="E6" s="33">
-        <v>20</v>
-      </c>
-      <c r="F6" s="33" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="35">
-        <v>70</v>
-      </c>
-      <c r="H6" s="33" t="s">
+      <c r="G6" s="33" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:7">
       <c r="A7" s="33">
         <v>7</v>
       </c>
@@ -5497,21 +5458,20 @@
       <c r="C7" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33">
+      <c r="D7" s="33">
         <v>45</v>
       </c>
-      <c r="F7" s="33" t="s">
+      <c r="E7" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="35">
+      <c r="F7" s="34">
         <v>202.5</v>
       </c>
-      <c r="H7" s="33" t="s">
+      <c r="G7" s="33" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:7">
       <c r="A8" s="33">
         <v>19</v>
       </c>
@@ -5522,22 +5482,19 @@
         <v>112</v>
       </c>
       <c r="D8" s="33">
+        <v>5</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="34">
         <v>30</v>
       </c>
-      <c r="E8" s="33">
-        <v>5</v>
-      </c>
-      <c r="F8" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="35">
-        <v>30</v>
-      </c>
-      <c r="H8" s="33" t="s">
+      <c r="G8" s="33" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:7">
       <c r="A9" s="33">
         <v>23</v>
       </c>
@@ -5548,22 +5505,19 @@
         <v>113</v>
       </c>
       <c r="D9" s="33">
+        <v>35</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="34">
         <v>90</v>
       </c>
-      <c r="E9" s="33">
-        <v>35</v>
-      </c>
-      <c r="F9" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="35">
-        <v>90</v>
-      </c>
-      <c r="H9" s="33" t="s">
+      <c r="G9" s="33" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:7">
       <c r="A10" s="33">
         <v>5</v>
       </c>
@@ -5574,22 +5528,19 @@
         <v>114</v>
       </c>
       <c r="D10" s="33">
+        <v>50</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="34">
         <v>500</v>
       </c>
-      <c r="E10" s="33">
-        <v>50</v>
-      </c>
-      <c r="F10" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="35">
-        <v>500</v>
-      </c>
-      <c r="H10" s="33" t="s">
+      <c r="G10" s="33" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:7">
       <c r="A11" s="33">
         <v>14</v>
       </c>
@@ -5600,22 +5551,19 @@
         <v>115</v>
       </c>
       <c r="D11" s="33">
+        <v>10</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="34">
         <v>130</v>
       </c>
-      <c r="E11" s="33">
-        <v>10</v>
-      </c>
-      <c r="F11" s="33" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" s="35">
-        <v>130</v>
-      </c>
-      <c r="H11" s="33" t="s">
+      <c r="G11" s="33" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:7">
       <c r="A12" s="33">
         <v>17</v>
       </c>
@@ -5626,22 +5574,19 @@
         <v>171</v>
       </c>
       <c r="D12" s="33">
+        <v>25</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="34">
         <v>950</v>
       </c>
-      <c r="E12" s="33">
-        <v>25</v>
-      </c>
-      <c r="F12" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="35">
-        <v>950</v>
-      </c>
-      <c r="H12" s="33" t="s">
+      <c r="G12" s="33" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:7">
       <c r="A13" s="33">
         <v>25</v>
       </c>
@@ -5652,22 +5597,19 @@
         <v>118</v>
       </c>
       <c r="D13" s="33">
+        <v>40</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="34">
         <v>90</v>
       </c>
-      <c r="E13" s="33">
-        <v>40</v>
-      </c>
-      <c r="F13" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="35">
-        <v>90</v>
-      </c>
-      <c r="H13" s="33" t="s">
+      <c r="G13" s="33" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:7">
       <c r="A14" s="33">
         <v>8</v>
       </c>
@@ -5678,22 +5620,19 @@
         <v>120</v>
       </c>
       <c r="D14" s="33">
+        <v>35</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="34">
         <v>120</v>
       </c>
-      <c r="E14" s="33">
-        <v>35</v>
-      </c>
-      <c r="F14" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" s="35">
-        <v>120</v>
-      </c>
-      <c r="H14" s="33" t="s">
+      <c r="G14" s="33" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:7">
       <c r="A15" s="33">
         <v>18</v>
       </c>
@@ -5704,22 +5643,19 @@
         <v>122</v>
       </c>
       <c r="D15" s="33">
+        <v>15</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="34">
         <v>150</v>
       </c>
-      <c r="E15" s="33">
-        <v>15</v>
-      </c>
-      <c r="F15" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="G15" s="35">
-        <v>150</v>
-      </c>
-      <c r="H15" s="33" t="s">
+      <c r="G15" s="33" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:7">
       <c r="A16" s="33">
         <v>16</v>
       </c>
@@ -5730,22 +5666,19 @@
         <v>124</v>
       </c>
       <c r="D16" s="33">
+        <v>20</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="34">
         <v>250</v>
       </c>
-      <c r="E16" s="33">
-        <v>20</v>
-      </c>
-      <c r="F16" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" s="35">
-        <v>250</v>
-      </c>
-      <c r="H16" s="33" t="s">
+      <c r="G16" s="33" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:7">
       <c r="A17" s="33">
         <v>21</v>
       </c>
@@ -5756,22 +5689,19 @@
         <v>125</v>
       </c>
       <c r="D17" s="33">
+        <v>35</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17" s="34">
         <v>50</v>
       </c>
-      <c r="E17" s="33">
-        <v>35</v>
-      </c>
-      <c r="F17" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="G17" s="35">
-        <v>50</v>
-      </c>
-      <c r="H17" s="33" t="s">
+      <c r="G17" s="33" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:7">
       <c r="A18" s="33">
         <v>20</v>
       </c>
@@ -5782,22 +5712,19 @@
         <v>127</v>
       </c>
       <c r="D18" s="33">
+        <v>15</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="34">
         <v>160</v>
       </c>
-      <c r="E18" s="33">
-        <v>15</v>
-      </c>
-      <c r="F18" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="G18" s="35">
-        <v>160</v>
-      </c>
-      <c r="H18" s="33" t="s">
+      <c r="G18" s="33" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:7">
       <c r="A19" s="33">
         <v>27</v>
       </c>
@@ -5808,22 +5735,19 @@
         <v>129</v>
       </c>
       <c r="D19" s="33">
+        <v>10</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="34">
         <v>980</v>
       </c>
-      <c r="E19" s="33">
-        <v>10</v>
-      </c>
-      <c r="F19" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19" s="35">
-        <v>980</v>
-      </c>
-      <c r="H19" s="33" t="s">
+      <c r="G19" s="33" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:7">
       <c r="A20" s="33">
         <v>1</v>
       </c>
@@ -5834,22 +5758,19 @@
         <v>130</v>
       </c>
       <c r="D20" s="33">
+        <v>15</v>
+      </c>
+      <c r="E20" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="34">
         <v>150</v>
       </c>
-      <c r="E20" s="33">
-        <v>15</v>
-      </c>
-      <c r="F20" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="35">
-        <v>150</v>
-      </c>
-      <c r="H20" s="33" t="s">
+      <c r="G20" s="33" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:7">
       <c r="A21" s="33">
         <v>14</v>
       </c>
@@ -5859,21 +5780,20 @@
       <c r="C21" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33">
+      <c r="D21" s="33">
         <v>10</v>
       </c>
-      <c r="F21" s="33" t="s">
+      <c r="E21" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="G21" s="35">
+      <c r="F21" s="34">
         <v>100</v>
       </c>
-      <c r="H21" s="33" t="s">
+      <c r="G21" s="33" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:7">
       <c r="A22" s="33">
         <v>14</v>
       </c>
@@ -5884,22 +5804,19 @@
         <v>133</v>
       </c>
       <c r="D22" s="33">
+        <v>50</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="34">
         <v>700</v>
       </c>
-      <c r="E22" s="33">
-        <v>50</v>
-      </c>
-      <c r="F22" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="G22" s="35">
-        <v>700</v>
-      </c>
-      <c r="H22" s="33" t="s">
+      <c r="G22" s="33" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:7">
       <c r="A23" s="33">
         <v>9</v>
       </c>
@@ -5910,22 +5827,19 @@
         <v>134</v>
       </c>
       <c r="D23" s="33">
+        <v>20</v>
+      </c>
+      <c r="E23" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="34">
         <v>80</v>
       </c>
-      <c r="E23" s="33">
-        <v>20</v>
-      </c>
-      <c r="F23" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" s="35">
-        <v>80</v>
-      </c>
-      <c r="H23" s="33" t="s">
+      <c r="G23" s="33" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:7">
       <c r="A24" s="33">
         <v>19</v>
       </c>
@@ -5936,22 +5850,19 @@
         <v>136</v>
       </c>
       <c r="D24" s="33">
+        <v>30</v>
+      </c>
+      <c r="E24" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="34">
         <v>150</v>
       </c>
-      <c r="E24" s="33">
-        <v>30</v>
-      </c>
-      <c r="F24" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="G24" s="35">
-        <v>150</v>
-      </c>
-      <c r="H24" s="33" t="s">
+      <c r="G24" s="33" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:7">
       <c r="A25" s="33">
         <v>21</v>
       </c>
@@ -5962,22 +5873,19 @@
         <v>125</v>
       </c>
       <c r="D25" s="33">
+        <v>35</v>
+      </c>
+      <c r="E25" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="F25" s="34">
         <v>50</v>
       </c>
-      <c r="E25" s="33">
-        <v>35</v>
-      </c>
-      <c r="F25" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="G25" s="35">
-        <v>50</v>
-      </c>
-      <c r="H25" s="33" t="s">
+      <c r="G25" s="33" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:7">
       <c r="A26" s="33">
         <v>29</v>
       </c>
@@ -5988,22 +5896,19 @@
         <v>137</v>
       </c>
       <c r="D26" s="33">
+        <v>45</v>
+      </c>
+      <c r="E26" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="34">
         <v>800</v>
       </c>
-      <c r="E26" s="33">
-        <v>45</v>
-      </c>
-      <c r="F26" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="G26" s="35">
-        <v>800</v>
-      </c>
-      <c r="H26" s="33" t="s">
+      <c r="G26" s="33" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:7">
       <c r="A27" s="33">
         <v>3</v>
       </c>
@@ -6013,21 +5918,20 @@
       <c r="C27" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33">
+      <c r="D27" s="33">
         <v>25</v>
       </c>
-      <c r="F27" s="33" t="s">
+      <c r="E27" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="G27" s="35">
+      <c r="F27" s="34">
         <v>76.666666666666671</v>
       </c>
-      <c r="H27" s="33" t="s">
+      <c r="G27" s="33" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:7">
       <c r="A28" s="33">
         <v>11</v>
       </c>
@@ -6038,22 +5942,19 @@
         <v>139</v>
       </c>
       <c r="D28" s="33">
+        <v>40</v>
+      </c>
+      <c r="E28" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="34">
         <v>400</v>
       </c>
-      <c r="E28" s="33">
-        <v>40</v>
-      </c>
-      <c r="F28" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="G28" s="35">
-        <v>400</v>
-      </c>
-      <c r="H28" s="33" t="s">
+      <c r="G28" s="33" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:7">
       <c r="A29" s="33">
         <v>16</v>
       </c>
@@ -6064,22 +5965,19 @@
         <v>124</v>
       </c>
       <c r="D29" s="33">
+        <v>20</v>
+      </c>
+      <c r="E29" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29" s="34">
         <v>250</v>
       </c>
-      <c r="E29" s="33">
-        <v>20</v>
-      </c>
-      <c r="F29" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="G29" s="35">
-        <v>250</v>
-      </c>
-      <c r="H29" s="33" t="s">
+      <c r="G29" s="33" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:7">
       <c r="A30" s="33">
         <v>7</v>
       </c>
@@ -6090,22 +5988,19 @@
         <v>140</v>
       </c>
       <c r="D30" s="33">
+        <v>30</v>
+      </c>
+      <c r="E30" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="34">
         <v>60</v>
       </c>
-      <c r="E30" s="33">
-        <v>30</v>
-      </c>
-      <c r="F30" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="35">
-        <v>60</v>
-      </c>
-      <c r="H30" s="33" t="s">
+      <c r="G30" s="33" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:7">
       <c r="A31" s="33">
         <v>13</v>
       </c>
@@ -6116,22 +6011,19 @@
         <v>141</v>
       </c>
       <c r="D31" s="33">
+        <v>10</v>
+      </c>
+      <c r="E31" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="34">
         <v>40</v>
       </c>
-      <c r="E31" s="33">
-        <v>10</v>
-      </c>
-      <c r="F31" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="G31" s="35">
-        <v>40</v>
-      </c>
-      <c r="H31" s="33" t="s">
+      <c r="G31" s="33" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:7">
       <c r="A32" s="33">
         <v>24</v>
       </c>
@@ -6142,22 +6034,19 @@
         <v>142</v>
       </c>
       <c r="D32" s="33">
+        <v>5</v>
+      </c>
+      <c r="E32" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="34">
         <v>130</v>
       </c>
-      <c r="E32" s="33">
-        <v>5</v>
-      </c>
-      <c r="F32" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="G32" s="35">
-        <v>130</v>
-      </c>
-      <c r="H32" s="33" t="s">
+      <c r="G32" s="33" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:7">
       <c r="A33" s="33">
         <v>2</v>
       </c>
@@ -6170,20 +6059,17 @@
       <c r="D33" s="33">
         <v>50</v>
       </c>
-      <c r="E33" s="33">
+      <c r="E33" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="34">
         <v>50</v>
       </c>
-      <c r="F33" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="35">
-        <v>50</v>
-      </c>
-      <c r="H33" s="33" t="s">
+      <c r="G33" s="33" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:7">
       <c r="A34" s="33">
         <v>17</v>
       </c>
@@ -6194,22 +6080,19 @@
         <v>171</v>
       </c>
       <c r="D34" s="33">
+        <v>25</v>
+      </c>
+      <c r="E34" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="34">
         <v>950</v>
       </c>
-      <c r="E34" s="33">
-        <v>25</v>
-      </c>
-      <c r="F34" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="G34" s="35">
-        <v>950</v>
-      </c>
-      <c r="H34" s="33" t="s">
+      <c r="G34" s="33" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:7">
       <c r="A35" s="33">
         <v>9</v>
       </c>
@@ -6220,22 +6103,19 @@
         <v>144</v>
       </c>
       <c r="D35" s="33">
+        <v>20</v>
+      </c>
+      <c r="E35" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="F35" s="34">
         <v>100</v>
       </c>
-      <c r="E35" s="33">
-        <v>20</v>
-      </c>
-      <c r="F35" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="G35" s="35">
-        <v>100</v>
-      </c>
-      <c r="H35" s="33" t="s">
+      <c r="G35" s="33" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:7">
       <c r="A36" s="26"/>
       <c r="B36" s="26"/>
       <c r="C36" s="26" t="s">
@@ -6244,27 +6124,12 @@
       <c r="D36" s="26"/>
       <c r="E36" s="26"/>
       <c r="F36" s="26"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="26" t="s">
+      <c r="G36" s="26" t="s">
         <v>194</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1">
-    <cfRule type="dataBar" priority="2">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFB628"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9634A395-5E6F-40AF-9367-12CC99B2B761}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G1:G34">
+  <conditionalFormatting sqref="F1:F34">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -6286,19 +6151,6 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9634A395-5E6F-40AF-9367-12CC99B2B761}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FFFFB628"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>D1</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{D9A33472-6315-42D6-A02F-16DFA5879172}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
@@ -6309,7 +6161,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>G1:G34</xm:sqref>
+          <xm:sqref>F1:F34</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
